--- a/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
+++ b/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Все занятия" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="По преподавателям" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Все занятия" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="По преподавателям" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Все занятия'!$A$1:$H$457</definedName>

--- a/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
+++ b/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
@@ -1375,7 +1375,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>18:10-19:00</t>
+          <t>18:30-19:20</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>18:10-19:00</t>
+          <t>18:30-19:20</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>18:10-19:00</t>
+          <t>18:30-19:20</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>18:10-19:00</t>
+          <t>18:30-19:20</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>17.10-18.00</t>
+          <t>17.25-18.15</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>16.10-17.00</t>
+          <t>16.20-17.10</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>17.10-18.00</t>
+          <t>17.25-18.15</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>17.10-18.00</t>
+          <t>17.25-18.15</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>16.10-17.00</t>
+          <t>16.20-17.10</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>17.10-18.00</t>
+          <t>17.25-18.15</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>17.10-18.00</t>
+          <t>17.25-18.15</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>17.10-18.00</t>
+          <t>17.25-18.15</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="E248" s="5" t="inlineStr">
@@ -11703,7 +11703,7 @@
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="E249" s="5" t="inlineStr">
@@ -13677,7 +13677,7 @@
       </c>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t>16.10-17.00</t>
+          <t>16.20-17.10</t>
         </is>
       </c>
       <c r="E296" s="5" t="inlineStr">
@@ -13845,7 +13845,7 @@
       </c>
       <c r="D300" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="E300" s="5" t="inlineStr">
@@ -16743,7 +16743,7 @@
       </c>
       <c r="D369" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="E369" s="5" t="inlineStr">
@@ -16785,7 +16785,7 @@
       </c>
       <c r="D370" s="5" t="inlineStr">
         <is>
-          <t>16.10-17.00</t>
+          <t>16.20-17.10</t>
         </is>
       </c>
       <c r="E370" s="5" t="inlineStr">
@@ -16953,7 +16953,7 @@
       </c>
       <c r="D374" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="E374" s="5" t="inlineStr">
@@ -17163,7 +17163,7 @@
       </c>
       <c r="D379" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="E379" s="5" t="inlineStr">
@@ -17205,7 +17205,7 @@
       </c>
       <c r="D380" s="5" t="inlineStr">
         <is>
-          <t>16.10-17.00</t>
+          <t>16.20-17.10</t>
         </is>
       </c>
       <c r="E380" s="5" t="inlineStr">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="D429" s="5" t="inlineStr">
         <is>
-          <t>16.10-17.00</t>
+          <t>16.20-17.10</t>
         </is>
       </c>
       <c r="E429" s="5" t="inlineStr">
@@ -19305,7 +19305,7 @@
       </c>
       <c r="D430" s="5" t="inlineStr">
         <is>
-          <t>17.10-18.00</t>
+          <t>17.25-18.15</t>
         </is>
       </c>
       <c r="E430" s="5" t="inlineStr">
@@ -20389,7 +20389,7 @@
       </c>
       <c r="D456" s="5" t="inlineStr">
         <is>
-          <t>16.10-17.00</t>
+          <t>16.20-17.10</t>
         </is>
       </c>
       <c r="E456" s="5" t="inlineStr">
@@ -20431,7 +20431,7 @@
       </c>
       <c r="D457" s="5" t="inlineStr">
         <is>
-          <t>18:10-19:00</t>
+          <t>18:30-19:20</t>
         </is>
       </c>
       <c r="E457" s="5" t="inlineStr">
@@ -21908,7 +21908,7 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -21940,7 +21940,7 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>17.10-18.00</t>
+          <t>17.25-18.15</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -22100,7 +22100,7 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -22292,7 +22292,7 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -22324,7 +22324,7 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>16.10-17.00</t>
+          <t>16.20-17.10</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -22459,7 +22459,7 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -22491,7 +22491,7 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -22523,7 +22523,7 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>17.10-18.00</t>
+          <t>17.25-18.15</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -22683,7 +22683,7 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -22715,7 +22715,7 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>17.10-18.00</t>
+          <t>17.25-18.15</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -22843,7 +22843,7 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>16.10-17.00</t>
+          <t>16.20-17.10</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -25171,7 +25171,7 @@
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
@@ -25203,7 +25203,7 @@
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>16.10-17.00</t>
+          <t>16.20-17.10</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
@@ -27048,7 +27048,7 @@
       </c>
       <c r="C232" s="5" t="inlineStr">
         <is>
-          <t>16.10-17.00</t>
+          <t>16.20-17.10</t>
         </is>
       </c>
       <c r="D232" s="5" t="inlineStr">
@@ -27080,7 +27080,7 @@
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
-          <t>17.10-18.00</t>
+          <t>17.25-18.15</t>
         </is>
       </c>
       <c r="D233" s="5" t="inlineStr">
@@ -30738,7 +30738,7 @@
       </c>
       <c r="C358" s="5" t="inlineStr">
         <is>
-          <t>16.10-17.00</t>
+          <t>16.20-17.10</t>
         </is>
       </c>
       <c r="D358" s="5" t="inlineStr">
@@ -30866,7 +30866,7 @@
       </c>
       <c r="C362" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="D362" s="5" t="inlineStr">
@@ -32910,7 +32910,7 @@
       </c>
       <c r="C433" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="D433" s="5" t="inlineStr">
@@ -33070,7 +33070,7 @@
       </c>
       <c r="C438" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="D438" s="5" t="inlineStr">
@@ -33230,7 +33230,7 @@
       </c>
       <c r="C443" s="5" t="inlineStr">
         <is>
-          <t>17.10-18.00</t>
+          <t>17.25-18.15</t>
         </is>
       </c>
       <c r="D443" s="5" t="inlineStr">
@@ -34371,7 +34371,7 @@
       </c>
       <c r="C484" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="D484" s="5" t="inlineStr">
@@ -34403,7 +34403,7 @@
       </c>
       <c r="C485" s="5" t="inlineStr">
         <is>
-          <t>16.10-17.00</t>
+          <t>16.20-17.10</t>
         </is>
       </c>
       <c r="D485" s="5" t="inlineStr">
@@ -34531,7 +34531,7 @@
       </c>
       <c r="C489" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="D489" s="5" t="inlineStr">
@@ -35238,7 +35238,7 @@
       </c>
       <c r="C520" s="5" t="inlineStr">
         <is>
-          <t>17.10-18.00</t>
+          <t>17.25-18.15</t>
         </is>
       </c>
       <c r="D520" s="5" t="inlineStr">
@@ -35909,7 +35909,7 @@
       </c>
       <c r="C557" s="5" t="inlineStr">
         <is>
-          <t>18:10-19:00</t>
+          <t>18:30-19:20</t>
         </is>
       </c>
       <c r="D557" s="5" t="inlineStr">
@@ -35941,7 +35941,7 @@
       </c>
       <c r="C558" s="5" t="inlineStr">
         <is>
-          <t>18:10-19:00</t>
+          <t>18:30-19:20</t>
         </is>
       </c>
       <c r="D558" s="5" t="inlineStr">
@@ -35973,7 +35973,7 @@
       </c>
       <c r="C559" s="5" t="inlineStr">
         <is>
-          <t>18:10-19:00</t>
+          <t>18:30-19:20</t>
         </is>
       </c>
       <c r="D559" s="5" t="inlineStr">
@@ -36005,7 +36005,7 @@
       </c>
       <c r="C560" s="5" t="inlineStr">
         <is>
-          <t>18:10-19:00</t>
+          <t>18:30-19:20</t>
         </is>
       </c>
       <c r="D560" s="5" t="inlineStr">
@@ -36076,7 +36076,7 @@
       </c>
       <c r="C564" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="D564" s="5" t="inlineStr">
@@ -36108,7 +36108,7 @@
       </c>
       <c r="C565" s="5" t="inlineStr">
         <is>
-          <t>15.10-16.00</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="D565" s="5" t="inlineStr">
@@ -36211,7 +36211,7 @@
       </c>
       <c r="C570" s="5" t="inlineStr">
         <is>
-          <t>16.10-17.00</t>
+          <t>16.20-17.10</t>
         </is>
       </c>
       <c r="D570" s="5" t="inlineStr">
@@ -36243,7 +36243,7 @@
       </c>
       <c r="C571" s="5" t="inlineStr">
         <is>
-          <t>18:10-19:00</t>
+          <t>18:30-19:20</t>
         </is>
       </c>
       <c r="D571" s="5" t="inlineStr">
@@ -36314,7 +36314,7 @@
       </c>
       <c r="C575" s="5" t="inlineStr">
         <is>
-          <t>17.10-18.00</t>
+          <t>17.25-18.15</t>
         </is>
       </c>
       <c r="D575" s="5" t="inlineStr">

--- a/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
+++ b/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Все занятия" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="По преподавателям" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Все занятия" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="По преподавателям" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Все занятия'!$A$1:$H$462</definedName>

--- a/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
+++ b/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Все занятия" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="По преподавателям" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Все занятия" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="По преподавателям" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Все занятия'!$A$1:$H$459</definedName>

--- a/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
+++ b/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Все занятия" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="По преподавателям" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Все занятия" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="По преподавателям" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Все занятия'!$A$1:$H$466</definedName>

--- a/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
+++ b/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
@@ -12491,37 +12491,37 @@
       </c>
       <c r="B268" s="5" t="inlineStr">
         <is>
-          <t>3 курс (бакалавриат)</t>
+          <t>2 курс (бакалавриат)</t>
         </is>
       </c>
       <c r="C268" s="5" t="inlineStr">
         <is>
-          <t>Среда</t>
+          <t>Понедельник</t>
         </is>
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>17.25-18.15</t>
+          <t>18:30-19:20</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
         <is>
-          <t>ИС-24-21 р/поис (21)+ (11) Типо +(4) Дот</t>
+          <t>ИС-25-21 (32) Программное обеспечение ИС</t>
         </is>
       </c>
       <c r="F268" s="8" t="inlineStr">
         <is>
-          <t>Разработка клиентских Web-приложений/Павлов С.В./лекция/онлайн</t>
+          <t>Технология программирования лекция Павлов С.В. Онлайн</t>
         </is>
       </c>
       <c r="G268" s="9" t="inlineStr">
         <is>
-          <t>3_kurs.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H268" s="9" t="inlineStr">
         <is>
-          <t>ИС-24-21, 22, Типо, Дот</t>
+          <t>ис,тии рус</t>
         </is>
       </c>
     </row>
@@ -12533,37 +12533,37 @@
       </c>
       <c r="B269" s="5" t="inlineStr">
         <is>
-          <t>Магистратура 2 курс</t>
+          <t>3 курс (бакалавриат)</t>
         </is>
       </c>
       <c r="C269" s="5" t="inlineStr">
         <is>
-          <t>Четверг</t>
+          <t>Среда</t>
         </is>
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>16.10-17.00</t>
+          <t>17.25-18.15</t>
         </is>
       </c>
       <c r="E269" s="5" t="inlineStr">
         <is>
-          <t>ИС-25 МН</t>
+          <t>ИС-24-21 р/поис (21)+ (11) Типо +(4) Дот</t>
         </is>
       </c>
       <c r="F269" s="8" t="inlineStr">
         <is>
-          <t>Технология разпознавания образов/лекция/Павлов С/ОНЛАЙН</t>
+          <t>Разработка клиентских Web-приложений/Павлов С.В./лекция/онлайн</t>
         </is>
       </c>
       <c r="G269" s="9" t="inlineStr">
         <is>
-          <t>magistratura_2kurs.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H269" s="9" t="inlineStr">
         <is>
-          <t>ФИТ</t>
+          <t>ИС-24-21, 22, Типо, Дот</t>
         </is>
       </c>
     </row>
@@ -12585,7 +12585,7 @@
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>17.10-18.00</t>
+          <t>16.10-17.00</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
@@ -12595,7 +12595,7 @@
       </c>
       <c r="F270" s="8" t="inlineStr">
         <is>
-          <t>Технология разпознавания образов/практика/Павлов С/ОНЛАЙН</t>
+          <t>Технология разпознавания образов/лекция/Павлов С/ОНЛАЙН</t>
         </is>
       </c>
       <c r="G270" s="9" t="inlineStr">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="B271" s="5" t="inlineStr">
         <is>
-          <t>2 курс (бакалавриат)</t>
+          <t>Магистратура 2 курс</t>
         </is>
       </c>
       <c r="C271" s="5" t="inlineStr">
@@ -12627,27 +12627,27 @@
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>20:40-21:30</t>
+          <t>17.10-18.00</t>
         </is>
       </c>
       <c r="E271" s="5" t="inlineStr">
         <is>
-          <t>ИС-25-21 (32) Программное обеспечение ИС</t>
+          <t>ИС-25 МН</t>
         </is>
       </c>
       <c r="F271" s="8" t="inlineStr">
         <is>
-          <t>Технология программирования лекция Павлов С.В. Онлайн</t>
+          <t>Технология разпознавания образов/практика/Павлов С/ОНЛАЙН</t>
         </is>
       </c>
       <c r="G271" s="9" t="inlineStr">
         <is>
-          <t>2_kurs.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
       <c r="H271" s="9" t="inlineStr">
         <is>
-          <t>ис,тии рус</t>
+          <t>ФИТ</t>
         </is>
       </c>
     </row>
@@ -14055,7 +14055,7 @@
       </c>
       <c r="D305" s="5" t="inlineStr">
         <is>
-          <t>10.40-11.30</t>
+          <t>13.05-13.55</t>
         </is>
       </c>
       <c r="E305" s="5" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="F305" s="8" t="inlineStr">
         <is>
-          <t>Алгоритмы и структуры данных ллекция Савдабаев Е 310-Б</t>
+          <t>Алгоритмы и структуры данных ллекция Савдабаев Е 303-Б</t>
         </is>
       </c>
       <c r="G305" s="9" t="inlineStr">
@@ -14569,7 +14569,7 @@
       </c>
       <c r="F317" s="8" t="inlineStr">
         <is>
-          <t>Интеллектуальный анализ данных/Сыдыбаева М./ лекция/514-1</t>
+          <t>Интеллектуальный анализ данных/Сыдыбаева М./ лекция/507-С</t>
         </is>
       </c>
       <c r="G317" s="9" t="inlineStr">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="F318" s="8" t="inlineStr">
         <is>
-          <t>Основы искусственного интеллекта практика Суйеналы А.А. 317-Б</t>
+          <t>Основы искусственного интеллекта практика Суйеналы А.А. 318-Б</t>
         </is>
       </c>
       <c r="G318" s="9" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="F447" s="8" t="inlineStr">
         <is>
-          <t>Основы кибербезопасности/Шайкулова А.А./лекция/501-Б</t>
+          <t>Основы кибербезопасности/Шайкулова А.А./лекция/501-С</t>
         </is>
       </c>
       <c r="G447" s="9" t="inlineStr">
@@ -20071,7 +20071,7 @@
       </c>
       <c r="F448" s="8" t="inlineStr">
         <is>
-          <t>Основы кибербезопасности/Шайкулова А.А./практика/501-Б</t>
+          <t>Основы кибербезопасности/Шайкулова А.А./практика/501-С</t>
         </is>
       </c>
       <c r="G448" s="9" t="inlineStr">
@@ -22009,7 +22009,7 @@
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>Основы кибербезопасности/Шайкулова А.А./лекция/501-Б</t>
+          <t>Основы кибербезопасности/Шайкулова А.А./лекция/501-С</t>
         </is>
       </c>
       <c r="F46" s="9" t="inlineStr">
@@ -22041,7 +22041,7 @@
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Основы кибербезопасности/Шайкулова А.А./практика/501-Б</t>
+          <t>Основы кибербезопасности/Шайкулова А.А./практика/501-С</t>
         </is>
       </c>
       <c r="F47" s="9" t="inlineStr">
@@ -29249,7 +29249,7 @@
       </c>
       <c r="E294" s="8" t="inlineStr">
         <is>
-          <t>Основы искусственного интеллекта практика Суйеналы А.А. 317-Б</t>
+          <t>Основы искусственного интеллекта практика Суйеналы А.А. 318-Б</t>
         </is>
       </c>
       <c r="F294" s="9" t="inlineStr">
@@ -31116,7 +31116,7 @@
       </c>
       <c r="C358" s="5" t="inlineStr">
         <is>
-          <t>10.40-11.30</t>
+          <t>13.05-13.55</t>
         </is>
       </c>
       <c r="D358" s="5" t="inlineStr">
@@ -31126,7 +31126,7 @@
       </c>
       <c r="E358" s="8" t="inlineStr">
         <is>
-          <t>Алгоритмы и структуры данных ллекция Савдабаев Е 310-Б</t>
+          <t>Алгоритмы и структуры данных ллекция Савдабаев Е 303-Б</t>
         </is>
       </c>
       <c r="F358" s="9" t="inlineStr">
@@ -35928,7 +35928,7 @@
       </c>
       <c r="E533" s="8" t="inlineStr">
         <is>
-          <t>Интеллектуальный анализ данных/Сыдыбаева М./ лекция/514-1</t>
+          <t>Интеллектуальный анализ данных/Сыдыбаева М./ лекция/507-С</t>
         </is>
       </c>
       <c r="F533" s="9" t="inlineStr">
@@ -36160,64 +36160,64 @@
     <row r="548">
       <c r="A548" s="5" t="inlineStr">
         <is>
-          <t>3 курс (бакалавриат)</t>
+          <t>2 курс (бакалавриат)</t>
         </is>
       </c>
       <c r="B548" s="5" t="inlineStr">
         <is>
-          <t>Среда</t>
+          <t>Понедельник</t>
         </is>
       </c>
       <c r="C548" s="5" t="inlineStr">
         <is>
-          <t>17.25-18.15</t>
+          <t>18:30-19:20</t>
         </is>
       </c>
       <c r="D548" s="5" t="inlineStr">
         <is>
-          <t>ИС-24-21 р/поис (21)+ (11) Типо +(4) Дот</t>
+          <t>ИС-25-21 (32) Программное обеспечение ИС</t>
         </is>
       </c>
       <c r="E548" s="8" t="inlineStr">
         <is>
-          <t>Разработка клиентских Web-приложений/Павлов С.В./лекция/онлайн</t>
+          <t>Технология программирования лекция Павлов С.В. Онлайн</t>
         </is>
       </c>
       <c r="F548" s="9" t="inlineStr">
         <is>
-          <t>3_kurs.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="5" t="inlineStr">
         <is>
-          <t>Магистратура 2 курс</t>
+          <t>3 курс (бакалавриат)</t>
         </is>
       </c>
       <c r="B549" s="5" t="inlineStr">
         <is>
-          <t>Четверг</t>
+          <t>Среда</t>
         </is>
       </c>
       <c r="C549" s="5" t="inlineStr">
         <is>
-          <t>16.10-17.00</t>
+          <t>17.25-18.15</t>
         </is>
       </c>
       <c r="D549" s="5" t="inlineStr">
         <is>
-          <t>ИС-25 МН</t>
+          <t>ИС-24-21 р/поис (21)+ (11) Типо +(4) Дот</t>
         </is>
       </c>
       <c r="E549" s="8" t="inlineStr">
         <is>
-          <t>Технология разпознавания образов/лекция/Павлов С/ОНЛАЙН</t>
+          <t>Разработка клиентских Web-приложений/Павлов С.В./лекция/онлайн</t>
         </is>
       </c>
       <c r="F549" s="9" t="inlineStr">
         <is>
-          <t>magistratura_2kurs.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -36234,7 +36234,7 @@
       </c>
       <c r="C550" s="5" t="inlineStr">
         <is>
-          <t>17.10-18.00</t>
+          <t>16.10-17.00</t>
         </is>
       </c>
       <c r="D550" s="5" t="inlineStr">
@@ -36244,7 +36244,7 @@
       </c>
       <c r="E550" s="8" t="inlineStr">
         <is>
-          <t>Технология разпознавания образов/практика/Павлов С/ОНЛАЙН</t>
+          <t>Технология разпознавания образов/лекция/Павлов С/ОНЛАЙН</t>
         </is>
       </c>
       <c r="F550" s="9" t="inlineStr">
@@ -36256,7 +36256,7 @@
     <row r="551">
       <c r="A551" s="5" t="inlineStr">
         <is>
-          <t>2 курс (бакалавриат)</t>
+          <t>Магистратура 2 курс</t>
         </is>
       </c>
       <c r="B551" s="5" t="inlineStr">
@@ -36266,22 +36266,22 @@
       </c>
       <c r="C551" s="5" t="inlineStr">
         <is>
-          <t>20:40-21:30</t>
+          <t>17.10-18.00</t>
         </is>
       </c>
       <c r="D551" s="5" t="inlineStr">
         <is>
-          <t>ИС-25-21 (32) Программное обеспечение ИС</t>
+          <t>ИС-25 МН</t>
         </is>
       </c>
       <c r="E551" s="8" t="inlineStr">
         <is>
-          <t>Технология программирования лекция Павлов С.В. Онлайн</t>
+          <t>Технология разпознавания образов/практика/Павлов С/ОНЛАЙН</t>
         </is>
       </c>
       <c r="F551" s="9" t="inlineStr">
         <is>
-          <t>2_kurs.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
     </row>

--- a/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
+++ b/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Все занятия" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="По преподавателям" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Все занятия" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="По преподавателям" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Все занятия'!$A$1:$H$466</definedName>

--- a/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
+++ b/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
@@ -6877,7 +6877,7 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>17.10-18.00</t>
+          <t>19.10-20.00</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="H134" s="9" t="inlineStr">
         <is>
-          <t>ФИТ</t>
+          <t>ФИТ (2)</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>17.10-18.00</t>
+          <t>19.10-20.00</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="H135" s="9" t="inlineStr">
         <is>
-          <t>ФИТ</t>
+          <t>ФИТ (2)</t>
         </is>
       </c>
     </row>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="H148" s="9" t="inlineStr">
         <is>
-          <t>ФИТ</t>
+          <t>ФИТ (2)</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="H149" s="9" t="inlineStr">
         <is>
-          <t>ФИТ</t>
+          <t>ФИТ (2)</t>
         </is>
       </c>
     </row>
@@ -8883,37 +8883,37 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>Магистратура 1 курс (научно-пед. направление)</t>
+          <t>3 курс (бакалавриат)</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>Понедельник</t>
+          <t>Вторник</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>13.05-13.55</t>
+          <t>10.40-11.30</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>ИС (МН)  2626 зимний прием,  26 осенний прием / КАЗ/О</t>
+          <t>ИС-24-21 р/поис (21)+ (11) Типо +(4) Дот</t>
         </is>
       </c>
       <c r="F182" s="8" t="inlineStr">
         <is>
-          <t>Анализ моделирование и проектирование информационных систем/ лек.зан./ Казангапова Б.А./ ауд.503-2С</t>
+          <t>Теория принятия решений/Казангапова Б.А./лекция/406-С</t>
         </is>
       </c>
       <c r="G182" s="9" t="inlineStr">
         <is>
-          <t>magistratura_nauchped.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H182" s="9" t="inlineStr">
         <is>
-          <t>ФИТ</t>
+          <t>ИС-24-21, 22, Типо, Дот</t>
         </is>
       </c>
     </row>
@@ -8925,37 +8925,37 @@
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>Магистратура 1 курс (научно-пед. направление)</t>
+          <t>3 курс (бакалавриат)</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>Понедельник</t>
+          <t>Среда</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>13.05-13.55</t>
+          <t>8.30-9.20</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
         <is>
-          <t>ИС(МН) 26 зимний прием,  26 осенний прием / РУС/О</t>
+          <t>ИС-24-21 р/поис (21)+ (11) Типо +(4) Дот</t>
         </is>
       </c>
       <c r="F183" s="8" t="inlineStr">
         <is>
-          <t>Анализ моделирование и проектирование информационных систем/ лек.зан./ Казангапова Б.А./ ауд.503-2С</t>
+          <t>Теория принятия решений/Казангапова Б.А./лабораторная/407-С</t>
         </is>
       </c>
       <c r="G183" s="9" t="inlineStr">
         <is>
-          <t>magistratura_nauchped.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H183" s="9" t="inlineStr">
         <is>
-          <t>ФИТ</t>
+          <t>ИС-24-21, 22, Типо, Дот</t>
         </is>
       </c>
     </row>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>Вторник</t>
+          <t>Среда</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="F184" s="8" t="inlineStr">
         <is>
-          <t>Теория принятия решений/Казангапова Б.А./лекция/406-С</t>
+          <t>Теория принятия решений/Казангапова Б.А./лабораторная/407-С</t>
         </is>
       </c>
       <c r="G184" s="9" t="inlineStr">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>Среда</t>
+          <t>Четверг</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="F185" s="8" t="inlineStr">
         <is>
-          <t>Теория принятия решений/Казангапова Б.А./лабораторная/407-С</t>
+          <t>Информационная безопасность и защита информации/Казангапова Б.А./лекция/406-С</t>
         </is>
       </c>
       <c r="G185" s="9" t="inlineStr">
@@ -9056,22 +9056,22 @@
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>Среда</t>
+          <t>Четверг</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>10.40-11.30</t>
+          <t>9.35-10.25</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>ИС-24-21 р/поис (21)+ (11) Типо +(4) Дот</t>
+          <t>ИС-24-22 р/о истт (19)</t>
         </is>
       </c>
       <c r="F186" s="8" t="inlineStr">
         <is>
-          <t>Теория принятия решений/Казангапова Б.А./лабораторная/407-С</t>
+          <t>Основы информационной безопасности/Казангапова Б.А./лекция/501-Б</t>
         </is>
       </c>
       <c r="G186" s="9" t="inlineStr">
@@ -9103,17 +9103,17 @@
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>8.30-9.20</t>
+          <t>10.40-11.30</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
         <is>
-          <t>ИС-24-21 р/поис (21)+ (11) Типо +(4) Дот</t>
+          <t>ИС-24-22 р/о истт (19)</t>
         </is>
       </c>
       <c r="F187" s="8" t="inlineStr">
         <is>
-          <t>Информационная безопасность и защита информации/Казангапова Б.А./лекция/406-С</t>
+          <t>Основы информационной безопасности/Казангапова Б.А./лабораторная/316-Б</t>
         </is>
       </c>
       <c r="G187" s="9" t="inlineStr">
@@ -9135,7 +9135,7 @@
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>3 курс (бакалавриат)</t>
+          <t>Магистратура 1 курс (профильное направление)</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
@@ -9145,27 +9145,27 @@
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>9.35-10.25</t>
+          <t>16.10-17.00</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>ИС-24-22 р/о истт (19)</t>
+          <t>ИС (3) МП, 26 осенний прием</t>
         </is>
       </c>
       <c r="F188" s="8" t="inlineStr">
         <is>
-          <t>Основы информационной безопасности/Казангапова Б.А./лекция/501-Б</t>
+          <t>Математические и инструментальные методы поддержки принятия решений / лек.зан./ Казангапова Б.А./ ауд.505-2Б</t>
         </is>
       </c>
       <c r="G188" s="9" t="inlineStr">
         <is>
-          <t>3_kurs.xlsx</t>
+          <t>magistratura_profil.xlsx</t>
         </is>
       </c>
       <c r="H188" s="9" t="inlineStr">
         <is>
-          <t>ИС-24-21, 22, Типо, Дот</t>
+          <t>ФИТ, ФЭиБ проф.нап.</t>
         </is>
       </c>
     </row>
@@ -9177,7 +9177,7 @@
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>3 курс (бакалавриат)</t>
+          <t>Магистратура 1 курс (профильное направление)</t>
         </is>
       </c>
       <c r="C189" s="5" t="inlineStr">
@@ -9187,27 +9187,27 @@
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>10.40-11.30</t>
+          <t>17.10-18.00</t>
         </is>
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>ИС-24-22 р/о истт (19)</t>
+          <t>ИС (3) МП, 26 осенний прием</t>
         </is>
       </c>
       <c r="F189" s="8" t="inlineStr">
         <is>
-          <t>Основы информационной безопасности/Казангапова Б.А./лабораторная/316-Б</t>
+          <t>Математические и инструментальные методы поддержки принятия решений / прак.зан./ Казангапова Б.А./ ауд.505-2Б</t>
         </is>
       </c>
       <c r="G189" s="9" t="inlineStr">
         <is>
-          <t>3_kurs.xlsx</t>
+          <t>magistratura_profil.xlsx</t>
         </is>
       </c>
       <c r="H189" s="9" t="inlineStr">
         <is>
-          <t>ИС-24-21, 22, Типо, Дот</t>
+          <t>ФИТ, ФЭиБ проф.нап.</t>
         </is>
       </c>
     </row>
@@ -9219,37 +9219,37 @@
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>Магистратура 1 курс (профильное направление)</t>
+          <t>3 курс (бакалавриат)</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>Четверг</t>
+          <t>Пятница</t>
         </is>
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>16.10-17.00</t>
+          <t>16.20-17.10</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>ИС (3) МП, 26 осенний прием</t>
+          <t>ИС-24-22 р/о истт (19)</t>
         </is>
       </c>
       <c r="F190" s="8" t="inlineStr">
         <is>
-          <t>Математические и инструментальные методы поддержки принятия решений / лек.зан./ Казангапова Б.А./ ауд.505-2Б</t>
+          <t>Основы исследования операций/Казангапова Б.А./лекция/501-Б</t>
         </is>
       </c>
       <c r="G190" s="9" t="inlineStr">
         <is>
-          <t>magistratura_profil.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H190" s="9" t="inlineStr">
         <is>
-          <t>ФИТ, ФЭиБ проф.нап.</t>
+          <t>ИС-24-21, 22, Типо, Дот</t>
         </is>
       </c>
     </row>
@@ -9261,37 +9261,37 @@
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>Магистратура 1 курс (профильное направление)</t>
+          <t>3 курс (бакалавриат)</t>
         </is>
       </c>
       <c r="C191" s="5" t="inlineStr">
         <is>
-          <t>Четверг</t>
+          <t>Пятница</t>
         </is>
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>17.10-18.00</t>
+          <t>17.25-18.15</t>
         </is>
       </c>
       <c r="E191" s="5" t="inlineStr">
         <is>
-          <t>ИС (3) МП, 26 осенний прием</t>
+          <t>ИС-24-22 р/о истт (19)</t>
         </is>
       </c>
       <c r="F191" s="8" t="inlineStr">
         <is>
-          <t>Математические и инструментальные методы поддержки принятия решений / прак.зан./ Казангапова Б.А./ ауд.505-2Б</t>
+          <t>Основы исследования операций/Казангапова Б.А./лабораторная/401-С</t>
         </is>
       </c>
       <c r="G191" s="9" t="inlineStr">
         <is>
-          <t>magistratura_profil.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H191" s="9" t="inlineStr">
         <is>
-          <t>ФИТ, ФЭиБ проф.нап.</t>
+          <t>ИС-24-21, 22, Типо, Дот</t>
         </is>
       </c>
     </row>
@@ -9313,7 +9313,7 @@
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>13.05-13.55</t>
+          <t>18.10-19.00</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="F192" s="8" t="inlineStr">
         <is>
-          <t>Анализ моделирование и проектирование информационных систем/ лаб.зан./ Казангапова Б.А./ ауд.507-2С</t>
+          <t>Анализ моделирование и проектирование информационных систем/ лек.зан./ Казангапова Б.А./ ауд.406-2С</t>
         </is>
       </c>
       <c r="G192" s="9" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H192" s="9" t="inlineStr">
         <is>
-          <t>ФИТ</t>
+          <t>ФИТ (2)</t>
         </is>
       </c>
     </row>
@@ -9355,7 +9355,7 @@
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>13.05-13.55</t>
+          <t>18.10-19.00</t>
         </is>
       </c>
       <c r="E193" s="5" t="inlineStr">
@@ -9365,7 +9365,7 @@
       </c>
       <c r="F193" s="8" t="inlineStr">
         <is>
-          <t>Анализ моделирование и проектирование информационных систем/ лаб.зан./ Казангапова Б.А./ ауд.507-2С</t>
+          <t>Анализ моделирование и проектирование информационных систем/ лек.зан./ Казангапова Б.А./ ауд.406-2С</t>
         </is>
       </c>
       <c r="G193" s="9" t="inlineStr">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="H193" s="9" t="inlineStr">
         <is>
-          <t>ФИТ</t>
+          <t>ФИТ (2)</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9387,7 @@
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>3 курс (бакалавриат)</t>
+          <t>Магистратура 1 курс (научно-пед. направление)</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
@@ -9397,27 +9397,27 @@
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>16.20-17.10</t>
+          <t>19.10-20.00</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>ИС-24-22 р/о истт (19)</t>
+          <t>ИС (МН)  2626 зимний прием,  26 осенний прием / КАЗ/О</t>
         </is>
       </c>
       <c r="F194" s="8" t="inlineStr">
         <is>
-          <t>Основы исследования операций/Казангапова Б.А./лекция/501-Б</t>
+          <t>Анализ моделирование и проектирование информационных систем/ лаб.зан./ Казангапова Б.А./ ауд.406-2С</t>
         </is>
       </c>
       <c r="G194" s="9" t="inlineStr">
         <is>
-          <t>3_kurs.xlsx</t>
+          <t>magistratura_nauchped.xlsx</t>
         </is>
       </c>
       <c r="H194" s="9" t="inlineStr">
         <is>
-          <t>ИС-24-21, 22, Типо, Дот</t>
+          <t>ФИТ (2)</t>
         </is>
       </c>
     </row>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>3 курс (бакалавриат)</t>
+          <t>Магистратура 1 курс (научно-пед. направление)</t>
         </is>
       </c>
       <c r="C195" s="5" t="inlineStr">
@@ -9439,27 +9439,27 @@
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>17.25-18.15</t>
+          <t>19.10-20.00</t>
         </is>
       </c>
       <c r="E195" s="5" t="inlineStr">
         <is>
-          <t>ИС-24-22 р/о истт (19)</t>
+          <t>ИС(МН) 26 зимний прием,  26 осенний прием / РУС/О</t>
         </is>
       </c>
       <c r="F195" s="8" t="inlineStr">
         <is>
-          <t>Основы исследования операций/Казангапова Б.А./лабораторная/401-С</t>
+          <t>Анализ моделирование и проектирование информационных систем/ лаб.зан./ Казангапова Б.А./ ауд.406-2С</t>
         </is>
       </c>
       <c r="G195" s="9" t="inlineStr">
         <is>
-          <t>3_kurs.xlsx</t>
+          <t>magistratura_nauchped.xlsx</t>
         </is>
       </c>
       <c r="H195" s="9" t="inlineStr">
         <is>
-          <t>ИС-24-21, 22, Типо, Дот</t>
+          <t>ФИТ (2)</t>
         </is>
       </c>
     </row>
@@ -13519,7 +13519,7 @@
       </c>
       <c r="F292" s="8" t="inlineStr">
         <is>
-          <t>Базы данных в информационных сиситемах Лабораторная Пайыз  425-Б</t>
+          <t>Базы данных в информационных сиситемах Лабораторная Пайыз  301-Б</t>
         </is>
       </c>
       <c r="G292" s="9" t="inlineStr">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="F293" s="8" t="inlineStr">
         <is>
-          <t>Базы данных в информационных сиситемах Лабораторная Пайыз  503-С</t>
+          <t>Базы данных в информационных сиситемах Лабораторная Пайыз  301-Б</t>
         </is>
       </c>
       <c r="G293" s="9" t="inlineStr">
@@ -21586,64 +21586,64 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Магистратура 1 курс (научно-пед. направление)</t>
+          <t>3 курс (бакалавриат)</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Понедельник</t>
+          <t>Вторник</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>13.05-13.55</t>
+          <t>10.40-11.30</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>ИС (МН)  2626 зимний прием,  26 осенний прием / КАЗ/О</t>
+          <t>ИС-24-21 р/поис (21)+ (11) Типо +(4) Дот</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Анализ моделирование и проектирование информационных систем/ лек.зан./ Казангапова Б.А./ ауд.503-2С</t>
+          <t>Теория принятия решений/Казангапова Б.А./лекция/406-С</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>magistratura_nauchped.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Магистратура 1 курс (научно-пед. направление)</t>
+          <t>3 курс (бакалавриат)</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Понедельник</t>
+          <t>Среда</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>13.05-13.55</t>
+          <t>8.30-9.20</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>ИС(МН) 26 зимний прием,  26 осенний прием / РУС/О</t>
+          <t>ИС-24-21 р/поис (21)+ (11) Типо +(4) Дот</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Анализ моделирование и проектирование информационных систем/ лек.зан./ Казангапова Б.А./ ауд.503-2С</t>
+          <t>Теория принятия решений/Казангапова Б.А./лабораторная/407-С</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>magistratura_nauchped.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21655,7 +21655,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Вторник</t>
+          <t>Среда</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -21670,7 +21670,7 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Теория принятия решений/Казангапова Б.А./лекция/406-С</t>
+          <t>Теория принятия решений/Казангапова Б.А./лабораторная/407-С</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
@@ -21687,7 +21687,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Среда</t>
+          <t>Четверг</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -21702,7 +21702,7 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Теория принятия решений/Казангапова Б.А./лабораторная/407-С</t>
+          <t>Информационная безопасность и защита информации/Казангапова Б.А./лекция/406-С</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
@@ -21719,22 +21719,22 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Среда</t>
+          <t>Четверг</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>10.40-11.30</t>
+          <t>9.35-10.25</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>ИС-24-21 р/поис (21)+ (11) Типо +(4) Дот</t>
+          <t>ИС-24-22 р/о истт (19)</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Теория принятия решений/Казангапова Б.А./лабораторная/407-С</t>
+          <t>Основы информационной безопасности/Казангапова Б.А./лекция/501-Б</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
@@ -21756,17 +21756,17 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>8.30-9.20</t>
+          <t>10.40-11.30</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>ИС-24-21 р/поис (21)+ (11) Типо +(4) Дот</t>
+          <t>ИС-24-22 р/о истт (19)</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Информационная безопасность и защита информации/Казангапова Б.А./лекция/406-С</t>
+          <t>Основы информационной безопасности/Казангапова Б.А./лабораторная/316-Б</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
@@ -21778,7 +21778,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>3 курс (бакалавриат)</t>
+          <t>Магистратура 1 курс (профильное направление)</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -21788,29 +21788,29 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>9.35-10.25</t>
+          <t>16.10-17.00</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>ИС-24-22 р/о истт (19)</t>
+          <t>ИС (3) МП, 26 осенний прием</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Основы информационной безопасности/Казангапова Б.А./лекция/501-Б</t>
+          <t>Математические и инструментальные методы поддержки принятия решений / лек.зан./ Казангапова Б.А./ ауд.505-2Б</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>3_kurs.xlsx</t>
+          <t>magistratura_profil.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>3 курс (бакалавриат)</t>
+          <t>Магистратура 1 курс (профильное направление)</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -21820,86 +21820,86 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>10.40-11.30</t>
+          <t>17.10-18.00</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>ИС-24-22 р/о истт (19)</t>
+          <t>ИС (3) МП, 26 осенний прием</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Основы информационной безопасности/Казангапова Б.А./лабораторная/316-Б</t>
+          <t>Математические и инструментальные методы поддержки принятия решений / прак.зан./ Казангапова Б.А./ ауд.505-2Б</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>3_kurs.xlsx</t>
+          <t>magistratura_profil.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Магистратура 1 курс (профильное направление)</t>
+          <t>3 курс (бакалавриат)</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Четверг</t>
+          <t>Пятница</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>16.10-17.00</t>
+          <t>16.20-17.10</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>ИС (3) МП, 26 осенний прием</t>
+          <t>ИС-24-22 р/о истт (19)</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Математические и инструментальные методы поддержки принятия решений / лек.зан./ Казангапова Б.А./ ауд.505-2Б</t>
+          <t>Основы исследования операций/Казангапова Б.А./лекция/501-Б</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>magistratura_profil.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Магистратура 1 курс (профильное направление)</t>
+          <t>3 курс (бакалавриат)</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Четверг</t>
+          <t>Пятница</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>17.10-18.00</t>
+          <t>17.25-18.15</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>ИС (3) МП, 26 осенний прием</t>
+          <t>ИС-24-22 р/о истт (19)</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Математические и инструментальные методы поддержки принятия решений / прак.зан./ Казангапова Б.А./ ауд.505-2Б</t>
+          <t>Основы исследования операций/Казангапова Б.А./лабораторная/401-С</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>magistratura_profil.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21916,7 +21916,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>13.05-13.55</t>
+          <t>18.10-19.00</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -21926,7 +21926,7 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Анализ моделирование и проектирование информационных систем/ лаб.зан./ Казангапова Б.А./ ауд.507-2С</t>
+          <t>Анализ моделирование и проектирование информационных систем/ лек.зан./ Казангапова Б.А./ ауд.406-2С</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
@@ -21948,7 +21948,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>13.05-13.55</t>
+          <t>18.10-19.00</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -21958,7 +21958,7 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Анализ моделирование и проектирование информационных систем/ лаб.зан./ Казангапова Б.А./ ауд.507-2С</t>
+          <t>Анализ моделирование и проектирование информационных систем/ лек.зан./ Казангапова Б.А./ ауд.406-2С</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
@@ -21970,7 +21970,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>3 курс (бакалавриат)</t>
+          <t>Магистратура 1 курс (научно-пед. направление)</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -21980,29 +21980,29 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>16.20-17.10</t>
+          <t>19.10-20.00</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>ИС-24-22 р/о истт (19)</t>
+          <t>ИС (МН)  2626 зимний прием,  26 осенний прием / КАЗ/О</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Основы исследования операций/Казангапова Б.А./лекция/501-Б</t>
+          <t>Анализ моделирование и проектирование информационных систем/ лаб.зан./ Казангапова Б.А./ ауд.406-2С</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>3_kurs.xlsx</t>
+          <t>magistratura_nauchped.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>3 курс (бакалавриат)</t>
+          <t>Магистратура 1 курс (научно-пед. направление)</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -22012,22 +22012,22 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>17.25-18.15</t>
+          <t>19.10-20.00</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>ИС-24-22 р/о истт (19)</t>
+          <t>ИС(МН) 26 зимний прием,  26 осенний прием / РУС/О</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Основы исследования операций/Казангапова Б.А./лабораторная/401-С</t>
+          <t>Анализ моделирование и проектирование информационных систем/ лаб.зан./ Казангапова Б.А./ ауд.406-2С</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>3_kurs.xlsx</t>
+          <t>magistratura_nauchped.xlsx</t>
         </is>
       </c>
     </row>
@@ -33485,7 +33485,7 @@
       </c>
       <c r="E420" s="8" t="inlineStr">
         <is>
-          <t>Базы данных в информационных сиситемах Лабораторная Пайыз  425-Б</t>
+          <t>Базы данных в информационных сиситемах Лабораторная Пайыз  301-Б</t>
         </is>
       </c>
       <c r="F420" s="9" t="inlineStr">
@@ -33517,7 +33517,7 @@
       </c>
       <c r="E421" s="8" t="inlineStr">
         <is>
-          <t>Базы данных в информационных сиситемах Лабораторная Пайыз  503-С</t>
+          <t>Базы данных в информационных сиситемах Лабораторная Пайыз  301-Б</t>
         </is>
       </c>
       <c r="F421" s="9" t="inlineStr">
@@ -34250,7 +34250,7 @@
       </c>
       <c r="C446" s="5" t="inlineStr">
         <is>
-          <t>17.10-18.00</t>
+          <t>19.10-20.00</t>
         </is>
       </c>
       <c r="D446" s="5" t="inlineStr">
@@ -34282,7 +34282,7 @@
       </c>
       <c r="C447" s="5" t="inlineStr">
         <is>
-          <t>17.10-18.00</t>
+          <t>19.10-20.00</t>
         </is>
       </c>
       <c r="D447" s="5" t="inlineStr">

--- a/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
+++ b/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Все занятия" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="По преподавателям" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Все занятия" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="По преподавателям" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Все занятия'!$A$1:$H$489</definedName>
@@ -9316,7 +9316,7 @@
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>16.20-17.10</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="E191" s="5" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="F191" s="8" t="inlineStr">
         <is>
-          <t>Основы исследования операций/Казангапова Б.А./лекция/501-Б</t>
+          <t>Основы исследования операций/Казангапова Б.А./лекция/504-С</t>
         </is>
       </c>
       <c r="G191" s="9" t="inlineStr">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>17.25-18.15</t>
+          <t>16.20-17.10</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="F192" s="8" t="inlineStr">
         <is>
-          <t>Основы исследования операций/Казангапова Б.А./лабораторная/401-С</t>
+          <t>Основы исследования операций/Казангапова Б.А./лабораторная/406-С</t>
         </is>
       </c>
       <c r="G192" s="9" t="inlineStr">
@@ -22722,7 +22722,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>16.20-17.10</t>
+          <t>15.15-16.05</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -22732,7 +22732,7 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Основы исследования операций/Казангапова Б.А./лекция/501-Б</t>
+          <t>Основы исследования операций/Казангапова Б.А./лекция/504-С</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
@@ -22754,7 +22754,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>17.25-18.15</t>
+          <t>16.20-17.10</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>Основы исследования операций/Казангапова Б.А./лабораторная/401-С</t>
+          <t>Основы исследования операций/Казангапова Б.А./лабораторная/406-С</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">

--- a/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
+++ b/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
@@ -9284,7 +9284,7 @@
       </c>
       <c r="F190" s="8" t="inlineStr">
         <is>
-          <t>Математические и инструментальные методы поддержки принятия решений / лек.зан./ Казангапова Б.А./ ауд. К-Класс ГУК</t>
+          <t>Математические и инструментальные методы поддержки принятия решений / лек.зан./ Казангапова Б.А./ ауд. Айти-РУМ  ГУК</t>
         </is>
       </c>
       <c r="G190" s="9" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="F191" s="8" t="inlineStr">
         <is>
-          <t>Математические и инструментальные методы поддержки принятия решений / прак.зан./ Казангапова Б.А./ ауд.К-класс ГУК</t>
+          <t>Математические и инструментальные методы поддержки принятия решений / прак.зан./ Казангапова Б.А./ ауд.АЙти РУМ ГУК</t>
         </is>
       </c>
       <c r="G191" s="9" t="inlineStr">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Математические и инструментальные методы поддержки принятия решений / лек.зан./ Казангапова Б.А./ ауд. К-Класс ГУК</t>
+          <t>Математические и инструментальные методы поддержки принятия решений / лек.зан./ Казангапова Б.А./ ауд. Айти-РУМ  ГУК</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr">
@@ -22742,7 +22742,7 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Математические и инструментальные методы поддержки принятия решений / прак.зан./ Казангапова Б.А./ ауд.К-класс ГУК</t>
+          <t>Математические и инструментальные методы поддержки принятия решений / прак.зан./ Казангапова Б.А./ ауд.АЙти РУМ ГУК</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr">
